--- a/Tabelas/casos_por_tipo.xlsx
+++ b/Tabelas/casos_por_tipo.xlsx
@@ -455,10 +455,10 @@
         </is>
       </c>
       <c r="C2" t="n">
-        <v>4743</v>
+        <v>5045</v>
       </c>
       <c r="D2" t="n">
-        <v>81.70999999999999</v>
+        <v>82.06</v>
       </c>
     </row>
     <row r="3">
@@ -471,10 +471,10 @@
         </is>
       </c>
       <c r="C3" t="n">
-        <v>1028</v>
+        <v>1033</v>
       </c>
       <c r="D3" t="n">
-        <v>17.71</v>
+        <v>16.8</v>
       </c>
     </row>
     <row r="4">
@@ -487,10 +487,10 @@
         </is>
       </c>
       <c r="C4" t="n">
-        <v>34</v>
+        <v>70</v>
       </c>
       <c r="D4" t="n">
-        <v>0.59</v>
+        <v>1.14</v>
       </c>
     </row>
     <row r="5">
